--- a/forms/trg/Formulir_TRG_adhentisrg.xlsx
+++ b/forms/trg/Formulir_TRG_adhentisrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,18 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Muhammad Yusuf, S.Pt., IPU</t>
+          <t>Prof. Dr. drg. Muhammad Harun Ahmad, M.Kes, Sp.KGA.,Subs.KKA(K).,FSASS</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Reproduksi Ternak</t>
+          <t>Pediatric Dentistry, Kraniofasial Anak</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -937,13 +933,17 @@
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3421-4384</t>
-        </is>
-      </c>
-      <c r="K5" s="12" t="n"/>
+          <t>0000-0003-3124-2064</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6011368</t>
+        </is>
+      </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>35116000200</t>
+          <t>57191342583</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. drg. Maria Tanumihardja</t>
+          <t>Prof. Dr. Ir. Muhammad Yusuf, S.Pt., IPU</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Konservasi gigi</t>
+          <t>Reproduksi Ternak</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,17 +982,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-1669-3609</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6201631</t>
-        </is>
-      </c>
+          <t>0000-0003-3421-4384</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>6602267792</t>
+          <t>35116000200</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1007,22 +1003,22 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ahmad Shuhud Irfani bin Zakaria</t>
+          <t>Prof. Dr. drg. Maria Tanumihardja</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Universiti Kebangsaan Malaysia</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Clinical and Health Sciences - Dental (Paediatric Dentistry)</t>
+          <t>Konservasi gigi</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1031,13 +1027,17 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-3715-9181</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="n"/>
+          <t>0000-0003-1669-3609</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>6201631</t>
+        </is>
+      </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>55519899000</t>
+          <t>6602267792</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1052,35 +1052,39 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. drg. A. St. Asmidar Anas, M.Kes</t>
+          <t>Dr. Ahmad Shuhud Irfani bin Zakaria</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universiti Kebangsaan Malaysia</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Oral Biologi</t>
+          <t>Clinical and Health Sciences - Dental (Paediatric Dentistry)</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>6692876</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="n"/>
+      <c r="J8" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-3715-9181</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>55519899000</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1093,12 +1097,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. drg. Rasmidar Samad, MS., FISDPH. FISPD</t>
+          <t>Dr. drg. A. St. Asmidar Anas, M.Kes</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1108,28 +1112,20 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Ilmu Kedokteran Gigi Masyarakat</t>
+          <t>Oral Biologi</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-1384-6967</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
-          <t>6006141</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>57201670892</t>
-        </is>
-      </c>
+          <t>6692876</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="n"/>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1142,12 +1138,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Rezky Oktaviyani Rusli</t>
+          <t>Prof. Dr. drg. Rasmidar Samad, MS., FISDPH. FISPD</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1155,14 +1151,30 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Ilmu Kedokteran Gigi Masyarakat</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-1384-6967</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
+        <is>
+          <t>6006141</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57201670892</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1175,12 +1187,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Giska Anandita Cahyani</t>
+          <t>Rezky Oktaviyani Rusli</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1208,12 +1220,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Nurul Mutmainnah</t>
+          <t>Giska Anandita Cahyani</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
@@ -1241,12 +1253,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Resti Allo Padang</t>
+          <t>Nurul Mutmainnah</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1272,10 +1284,26 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Resti Allo Padang</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>The Adhesive Dentistry Research Group is committed to developing dental materials science and its applications. By integrating innovative technologies such as nanocalcium and nanochitosan derived from natural sources, the group aims to address challenges in bone and tooth regeneration. Through a multidisciplinary approach, the team focuses on safety, effectiveness, and practical applications to improve oral health worldwide.</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
@@ -1283,7 +1311,11 @@
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1472,15 +1504,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
